--- a/Program/master_lines.xlsx
+++ b/Program/master_lines.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Master Lines" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lines" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Lines'!$A$1:$BK$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lines'!$A$1:$BL$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,19 +68,19 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
+      <left style="thick">
         <color rgb="FF4169E1"/>
-      </right>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
+      <left/>
+      <right style="thick">
         <color rgb="FF4169E1"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -109,13 +109,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -198,9 +198,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterLinesTable" displayName="MasterLinesTable" ref="A1:BK17" headerRowCount="1">
-  <autoFilter ref="A1:BK17"/>
-  <tableColumns count="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LinesTable" displayName="LinesTable" ref="A1:BL17" headerRowCount="1">
+  <autoFilter ref="A1:BL17"/>
+  <tableColumns count="64">
     <tableColumn id="1" name="Line Number"/>
     <tableColumn id="2" name="Extra Vacation Days"/>
     <tableColumn id="3" name="Sun, May 21"/>
@@ -264,6 +264,7 @@
     <tableColumn id="61" name="Total DO"/>
     <tableColumn id="62" name="% tickets paid"/>
     <tableColumn id="63" name="Premium"/>
+    <tableColumn id="64" name="Start bid off"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -558,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK17"/>
+  <dimension ref="A1:BL17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -624,6 +625,7 @@
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="16" customWidth="1" min="62" max="62"/>
     <col width="9" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -637,7 +639,7 @@
           <t>Extra Vacation Days</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Sun, May 21</t>
         </is>
@@ -692,7 +694,7 @@
           <t>Wed, May 31</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Thu, Jun 1</t>
         </is>
@@ -727,7 +729,7 @@
           <t>Wed, Jun 7</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Thu, Jun 8</t>
         </is>
@@ -940,6 +942,11 @@
       <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Premium</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Start bid off</t>
         </is>
       </c>
     </row>
@@ -950,7 +957,7 @@
       <c r="B2" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
@@ -996,7 +1003,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr"/>
       <c r="T2" s="1" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="1" t="inlineStr"/>
       <c r="X2" s="6" t="inlineStr">
@@ -1131,6 +1138,9 @@
       <c r="BK2" t="n">
         <v>0</v>
       </c>
+      <c r="BL2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" t="n">
@@ -1139,7 +1149,7 @@
       <c r="B3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
@@ -1185,7 +1195,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
       <c r="W3" s="1" t="inlineStr"/>
       <c r="X3" s="6" t="inlineStr">
@@ -1320,6 +1330,9 @@
       <c r="BK3" t="n">
         <v>0</v>
       </c>
+      <c r="BL3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" t="n">
@@ -1328,7 +1341,7 @@
       <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr"/>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
@@ -1359,7 +1372,7 @@
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
@@ -1489,6 +1502,9 @@
       <c r="BK4" t="n">
         <v>0</v>
       </c>
+      <c r="BL4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" t="n">
@@ -1497,7 +1513,7 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
       <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -1662,6 +1678,9 @@
       <c r="BK5" t="n">
         <v>0</v>
       </c>
+      <c r="BL5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" t="n">
@@ -1670,7 +1689,7 @@
       <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
       <c r="D6" s="1" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1743,7 @@
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
       <c r="W6" s="1" t="inlineStr"/>
       <c r="X6" s="1" t="inlineStr"/>
@@ -1851,6 +1870,9 @@
       <c r="BK6" t="n">
         <v>0</v>
       </c>
+      <c r="BL6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" t="n">
@@ -1859,7 +1881,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>RA</t>
@@ -2040,6 +2062,9 @@
       <c r="BK7" t="n">
         <v>0</v>
       </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" t="n">
@@ -2048,7 +2073,7 @@
       <c r="B8" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>{291SDF-</t>
         </is>
@@ -2083,14 +2108,14 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr"/>
       <c r="T8" s="1" t="inlineStr"/>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
       <c r="W8" s="1" t="inlineStr"/>
       <c r="X8" s="6" t="inlineStr">
@@ -2225,6 +2250,9 @@
       <c r="BK8" t="n">
         <v>0</v>
       </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" t="n">
@@ -2233,7 +2261,7 @@
       <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>{307SDF-</t>
         </is>
@@ -2272,7 +2300,7 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr">
@@ -2418,6 +2446,9 @@
       <c r="BK9" t="n">
         <v>0</v>
       </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" t="n">
@@ -2426,7 +2457,7 @@
       <c r="B10" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>{395SDF-(DH DL)[ATL25.5]</t>
         </is>
@@ -2469,14 +2500,14 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr"/>
       <c r="T10" s="1" t="inlineStr"/>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="1" t="inlineStr"/>
       <c r="W10" s="1" t="inlineStr"/>
       <c r="X10" s="6" t="inlineStr">
@@ -2661,6 +2692,9 @@
         <v>75</v>
       </c>
       <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2671,7 +2705,7 @@
       <c r="B11" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>VTO</t>
         </is>
@@ -2900,6 +2934,9 @@
       <c r="BK11" t="n">
         <v>439</v>
       </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" t="n">
@@ -2908,7 +2945,7 @@
       <c r="B12" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>VTO</t>
         </is>
@@ -3199,6 +3236,9 @@
         <v>0</v>
       </c>
       <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3209,7 +3249,7 @@
       <c r="B13" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3263,7 +3303,7 @@
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr"/>
       <c r="T13" s="1" t="inlineStr"/>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr"/>
       <c r="W13" s="1" t="inlineStr"/>
       <c r="X13" s="6" t="inlineStr">
@@ -3390,6 +3430,9 @@
       <c r="BK13" t="n">
         <v>0</v>
       </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" t="n">
@@ -3398,7 +3441,7 @@
       <c r="B14" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -3437,7 +3480,7 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr">
@@ -3579,6 +3622,9 @@
       <c r="BK14" t="n">
         <v>0</v>
       </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" t="n">
@@ -3587,7 +3633,7 @@
       <c r="B15" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3626,7 +3672,7 @@
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="6" t="inlineStr">
@@ -3768,6 +3814,9 @@
       <c r="BK15" t="n">
         <v>0</v>
       </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" t="n">
@@ -3776,7 +3825,7 @@
       <c r="B16" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3838,7 +3887,7 @@
       </c>
       <c r="S16" s="1" t="inlineStr"/>
       <c r="T16" s="1" t="inlineStr"/>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr"/>
       <c r="W16" s="1" t="inlineStr"/>
       <c r="X16" s="1" t="inlineStr"/>
@@ -3957,6 +4006,9 @@
       <c r="BK16" t="n">
         <v>0</v>
       </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" t="n">
@@ -3965,7 +4017,7 @@
       <c r="B17" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>VOR</t>
         </is>
@@ -4258,9 +4310,12 @@
       <c r="BK17" t="n">
         <v>0</v>
       </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BK17"/>
+  <autoFilter ref="A1:BL17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Program/master_lines.xlsx
+++ b/Program/master_lines.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Lines" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Master Lines" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lines'!$A$1:$BL$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Lines'!$A$1:$BM$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,8 +27,12 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,8 +44,18 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF800080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -51,7 +65,7 @@
     </border>
     <border>
       <left style="thick">
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFFA500"/>
       </left>
       <right/>
       <top/>
@@ -60,16 +74,25 @@
     </border>
     <border>
       <left/>
-      <right style="thick">
-        <color rgb="FFFF0000"/>
+      <right style="mediumDashed">
+        <color rgb="FFFFA500"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left style="mediumDashed">
+        <color rgb="FF800080"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
-        <color rgb="FF4169E1"/>
+        <color rgb="FF800080"/>
       </left>
       <right/>
       <top/>
@@ -78,8 +101,8 @@
     </border>
     <border>
       <left/>
-      <right style="thick">
-        <color rgb="FF4169E1"/>
+      <right style="mediumDashed">
+        <color rgb="FF800080"/>
       </right>
       <top/>
       <bottom/>
@@ -89,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,28 +120,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -198,9 +236,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LinesTable" displayName="LinesTable" ref="A1:BL17" headerRowCount="1">
-  <autoFilter ref="A1:BL17"/>
-  <tableColumns count="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterLinesTable" displayName="MasterLinesTable" ref="A1:BM17" headerRowCount="1">
+  <autoFilter ref="A1:BM17"/>
+  <tableColumns count="65">
     <tableColumn id="1" name="Line Number"/>
     <tableColumn id="2" name="Extra Vacation Days"/>
     <tableColumn id="3" name="Sun, May 21"/>
@@ -263,8 +301,9 @@
     <tableColumn id="60" name="Blockiness"/>
     <tableColumn id="61" name="Total DO"/>
     <tableColumn id="62" name="% tickets paid"/>
-    <tableColumn id="63" name="Premium"/>
-    <tableColumn id="64" name="Start bid off"/>
+    <tableColumn id="63" name="Total CT"/>
+    <tableColumn id="64" name="Premium"/>
+    <tableColumn id="65" name="Start bid off"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -559,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL17"/>
+  <dimension ref="A1:BM17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -624,8 +663,9 @@
     <col width="19" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="16" customWidth="1" min="62" max="62"/>
-    <col width="9" customWidth="1" min="63" max="63"/>
-    <col width="15" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="9" customWidth="1" min="64" max="64"/>
+    <col width="15" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -639,7 +679,7 @@
           <t>Extra Vacation Days</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Sun, May 21</t>
         </is>
@@ -694,42 +734,42 @@
           <t>Wed, May 31</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Thu, Jun 1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Fri, Jun 2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Sat, Jun 3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Sun, Jun 4</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>Mon, Jun 5</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>Tue, Jun 6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="6" t="inlineStr">
         <is>
           <t>Wed, Jun 7</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>Thu, Jun 8</t>
         </is>
@@ -789,7 +829,7 @@
           <t>Mon, Jun 19</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Tue, Jun 20</t>
         </is>
@@ -839,7 +879,7 @@
           <t>Thu, Jun 29</t>
         </is>
       </c>
-      <c r="AQ1" s="5" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Fri, Jun 30</t>
         </is>
@@ -941,10 +981,15 @@
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
+          <t>Total CT</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Start bid off</t>
         </is>
@@ -957,118 +1002,118 @@
       <c r="B2" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
-      <c r="R2" s="1" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr"/>
       <c r="T2" s="1" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
+      <c r="U2" s="11" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="1" t="inlineStr"/>
-      <c r="X2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="Y2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="Z2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AA2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AB2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AC2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AD2" s="6" t="inlineStr">
+      <c r="X2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="Y2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="Z2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AA2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AB2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AC2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AD2" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
       </c>
       <c r="AE2" s="1" t="inlineStr"/>
       <c r="AF2" s="1" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
+      <c r="AG2" s="1" t="inlineStr"/>
       <c r="AH2" s="1" t="inlineStr"/>
       <c r="AI2" s="1" t="inlineStr"/>
       <c r="AJ2" s="1" t="inlineStr"/>
       <c r="AK2" s="1" t="inlineStr"/>
-      <c r="AL2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AM2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AN2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AO2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AP2" s="6" t="inlineStr">
+      <c r="AL2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AM2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AN2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AO2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AP2" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -1078,7 +1123,7 @@
           <t>SB</t>
         </is>
       </c>
-      <c r="AR2" s="6" t="inlineStr">
+      <c r="AR2" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -1090,37 +1135,37 @@
       <c r="AW2" s="1" t="inlineStr"/>
       <c r="AX2" s="1" t="inlineStr"/>
       <c r="AY2" s="1" t="inlineStr"/>
-      <c r="AZ2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="BA2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="BB2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="BC2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="BD2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="BE2" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="BF2" s="6" t="inlineStr">
+      <c r="AZ2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="BA2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="BB2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="BC2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="BD2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="BE2" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="BF2" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -1139,6 +1184,9 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1149,118 +1197,118 @@
       <c r="B3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr"/>
-      <c r="R3" s="1" t="inlineStr"/>
+      <c r="R3" s="10" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr"/>
+      <c r="U3" s="11" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
       <c r="W3" s="1" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="Y3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="Z3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AA3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AB3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AC3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AD3" s="6" t="inlineStr">
+      <c r="X3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="Y3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="Z3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AA3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AB3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AC3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AD3" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
       <c r="AE3" s="1" t="inlineStr"/>
       <c r="AF3" s="1" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AG3" s="1" t="inlineStr"/>
       <c r="AH3" s="1" t="inlineStr"/>
       <c r="AI3" s="1" t="inlineStr"/>
       <c r="AJ3" s="1" t="inlineStr"/>
       <c r="AK3" s="1" t="inlineStr"/>
-      <c r="AL3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AM3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AN3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AO3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AP3" s="6" t="inlineStr">
+      <c r="AL3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AM3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AN3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AO3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AP3" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -1270,7 +1318,7 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="AR3" s="6" t="inlineStr">
+      <c r="AR3" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -1282,37 +1330,37 @@
       <c r="AW3" s="1" t="inlineStr"/>
       <c r="AX3" s="1" t="inlineStr"/>
       <c r="AY3" s="1" t="inlineStr"/>
-      <c r="AZ3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BA3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BB3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BC3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BD3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BE3" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BF3" s="6" t="inlineStr">
+      <c r="AZ3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BA3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BB3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BC3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BD3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BE3" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BF3" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -1331,6 +1379,9 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1341,29 +1392,29 @@
       <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="1" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>{4SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>{4SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>{4SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>{4SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>{31SDF-MKE-SDF}</t>
         </is>
@@ -1372,22 +1423,22 @@
       <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="12" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
-      <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="R4" s="10" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="U4" s="13" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
@@ -1396,22 +1447,22 @@
       <c r="W4" s="1" t="inlineStr"/>
       <c r="X4" s="1" t="inlineStr"/>
       <c r="Y4" s="1" t="inlineStr"/>
-      <c r="Z4" s="6" t="inlineStr">
+      <c r="Z4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="AA4" s="6" t="inlineStr">
+      <c r="AA4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="AB4" s="6" t="inlineStr">
+      <c r="AB4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AC4" s="8" t="inlineStr">
         <is>
           <t>{65SDF-EWR-SDF}</t>
         </is>
@@ -1419,24 +1470,24 @@
       <c r="AD4" s="1" t="inlineStr"/>
       <c r="AE4" s="1" t="inlineStr"/>
       <c r="AF4" s="1" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AG4" s="1" t="inlineStr"/>
       <c r="AH4" s="1" t="inlineStr"/>
       <c r="AI4" s="1" t="inlineStr"/>
       <c r="AJ4" s="1" t="inlineStr"/>
       <c r="AK4" s="1" t="inlineStr"/>
       <c r="AL4" s="1" t="inlineStr"/>
       <c r="AM4" s="1" t="inlineStr"/>
-      <c r="AN4" s="6" t="inlineStr">
+      <c r="AN4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="AO4" s="6" t="inlineStr">
+      <c r="AO4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="AP4" s="6" t="inlineStr">
+      <c r="AP4" s="8" t="inlineStr">
         <is>
           <t>{5SDF-EWR-SDF}</t>
         </is>
@@ -1450,17 +1501,17 @@
       <c r="AS4" s="1" t="inlineStr"/>
       <c r="AT4" s="1" t="inlineStr"/>
       <c r="AU4" s="1" t="inlineStr"/>
-      <c r="AV4" s="6" t="inlineStr">
+      <c r="AV4" s="8" t="inlineStr">
         <is>
           <t>{49SDF-JFK-SDF}</t>
         </is>
       </c>
-      <c r="AW4" s="6" t="inlineStr">
+      <c r="AW4" s="8" t="inlineStr">
         <is>
           <t>{3SDF-JFK-SDF}</t>
         </is>
       </c>
-      <c r="AX4" s="6" t="inlineStr">
+      <c r="AX4" s="8" t="inlineStr">
         <is>
           <t>{65SDF-EWR-SDF}</t>
         </is>
@@ -1468,22 +1519,22 @@
       <c r="AY4" s="1" t="inlineStr"/>
       <c r="AZ4" s="1" t="inlineStr"/>
       <c r="BA4" s="1" t="inlineStr"/>
-      <c r="BB4" s="6" t="inlineStr">
+      <c r="BB4" s="8" t="inlineStr">
         <is>
           <t>{6SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="BC4" s="6" t="inlineStr">
+      <c r="BC4" s="8" t="inlineStr">
         <is>
           <t>{6SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="BD4" s="6" t="inlineStr">
+      <c r="BD4" s="8" t="inlineStr">
         <is>
           <t>{6SDF-EWR-SDF}</t>
         </is>
       </c>
-      <c r="BE4" s="6" t="inlineStr">
+      <c r="BE4" s="8" t="inlineStr">
         <is>
           <t>{6SDF-EWR-SDF}</t>
         </is>
@@ -1500,9 +1551,12 @@
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>138.57</v>
       </c>
       <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1513,19 +1567,19 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="1" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>{7SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>{7SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>{14SDF-MCO-SDF}</t>
         </is>
@@ -1535,12 +1589,12 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
@@ -1548,23 +1602,23 @@
       <c r="O5" s="1" t="inlineStr"/>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
-      <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="R5" s="10" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="U5" s="9" t="inlineStr">
+      <c r="U5" s="13" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="V5" s="6" t="inlineStr">
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>{34SDF-PHL-SDF}</t>
         </is>
@@ -1572,17 +1626,17 @@
       <c r="W5" s="1" t="inlineStr"/>
       <c r="X5" s="1" t="inlineStr"/>
       <c r="Y5" s="1" t="inlineStr"/>
-      <c r="Z5" s="6" t="inlineStr">
+      <c r="Z5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="AA5" s="6" t="inlineStr">
+      <c r="AA5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="AB5" s="6" t="inlineStr">
+      <c r="AB5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
@@ -1591,17 +1645,17 @@
       <c r="AD5" s="1" t="inlineStr"/>
       <c r="AE5" s="1" t="inlineStr"/>
       <c r="AF5" s="1" t="inlineStr"/>
-      <c r="AG5" s="10" t="inlineStr">
+      <c r="AG5" s="8" t="inlineStr">
         <is>
           <t>{22SDF-IAH-SDF}</t>
         </is>
       </c>
-      <c r="AH5" s="6" t="inlineStr">
+      <c r="AH5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="AI5" s="6" t="inlineStr">
+      <c r="AI5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
@@ -1610,28 +1664,28 @@
       <c r="AK5" s="1" t="inlineStr"/>
       <c r="AL5" s="1" t="inlineStr"/>
       <c r="AM5" s="1" t="inlineStr"/>
-      <c r="AN5" s="6" t="inlineStr">
+      <c r="AN5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="AO5" s="6" t="inlineStr">
+      <c r="AO5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="AP5" s="6" t="inlineStr">
+      <c r="AP5" s="8" t="inlineStr">
         <is>
           <t>{8SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="AQ5" s="5" t="inlineStr"/>
+      <c r="AQ5" s="1" t="inlineStr"/>
       <c r="AR5" s="1" t="inlineStr"/>
       <c r="AS5" s="1" t="inlineStr"/>
       <c r="AT5" s="1" t="inlineStr"/>
       <c r="AU5" s="1" t="inlineStr"/>
       <c r="AV5" s="1" t="inlineStr"/>
-      <c r="AW5" s="6" t="inlineStr">
+      <c r="AW5" s="8" t="inlineStr">
         <is>
           <t>{9SDF-MIA-SDF}</t>
         </is>
@@ -1640,27 +1694,27 @@
       <c r="AY5" s="1" t="inlineStr"/>
       <c r="AZ5" s="1" t="inlineStr"/>
       <c r="BA5" s="1" t="inlineStr"/>
-      <c r="BB5" s="6" t="inlineStr">
+      <c r="BB5" s="8" t="inlineStr">
         <is>
           <t>{9SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="BC5" s="6" t="inlineStr">
+      <c r="BC5" s="8" t="inlineStr">
         <is>
           <t>{9SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="BD5" s="6" t="inlineStr">
+      <c r="BD5" s="8" t="inlineStr">
         <is>
           <t>{9SDF-MIA-SDF}</t>
         </is>
       </c>
-      <c r="BE5" s="6" t="inlineStr">
+      <c r="BE5" s="8" t="inlineStr">
         <is>
           <t>{34SDF-PHL-SDF}</t>
         </is>
       </c>
-      <c r="BF5" s="6" t="inlineStr">
+      <c r="BF5" s="8" t="inlineStr">
         <is>
           <t>{46SDF-DTW-(DH DL)SDF}</t>
         </is>
@@ -1676,9 +1730,12 @@
         <v>2.1</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1689,29 +1746,29 @@
       <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1719,79 +1776,79 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr"/>
-      <c r="R6" s="1" t="inlineStr"/>
+      <c r="R6" s="10" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr"/>
+      <c r="U6" s="11" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
       <c r="W6" s="1" t="inlineStr"/>
       <c r="X6" s="1" t="inlineStr"/>
       <c r="Y6" s="1" t="inlineStr"/>
-      <c r="Z6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AA6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AC6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AD6" s="6" t="inlineStr">
+      <c r="Z6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AA6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AB6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AC6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AD6" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
       </c>
       <c r="AE6" s="1" t="inlineStr"/>
       <c r="AF6" s="1" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AI6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AJ6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AK6" s="6" t="inlineStr">
+      <c r="AG6" s="1" t="inlineStr"/>
+      <c r="AH6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AI6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AJ6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AK6" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1799,12 +1856,12 @@
       <c r="AL6" s="1" t="inlineStr"/>
       <c r="AM6" s="1" t="inlineStr"/>
       <c r="AN6" s="1" t="inlineStr"/>
-      <c r="AO6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AP6" s="6" t="inlineStr">
+      <c r="AO6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AP6" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1814,12 +1871,12 @@
           <t>RA</t>
         </is>
       </c>
-      <c r="AR6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AS6" s="6" t="inlineStr">
+      <c r="AR6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AS6" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1832,27 +1889,27 @@
       <c r="AY6" s="1" t="inlineStr"/>
       <c r="AZ6" s="1" t="inlineStr"/>
       <c r="BA6" s="1" t="inlineStr"/>
-      <c r="BB6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="BC6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="BD6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="BE6" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="BF6" s="6" t="inlineStr">
+      <c r="BB6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="BC6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="BD6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="BE6" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="BF6" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1871,6 +1928,9 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1881,28 +1941,28 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1910,50 +1970,50 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
-      <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="U7" s="9" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="W7" s="6" t="inlineStr">
+      <c r="R7" s="10" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="U7" s="13" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1966,27 +2026,27 @@
       <c r="AC7" s="1" t="inlineStr"/>
       <c r="AD7" s="1" t="inlineStr"/>
       <c r="AE7" s="1" t="inlineStr"/>
-      <c r="AF7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AG7" s="10" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AH7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AI7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AJ7" s="6" t="inlineStr">
+      <c r="AF7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AG7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AH7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AI7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AJ7" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -1994,17 +2054,17 @@
       <c r="AK7" s="1" t="inlineStr"/>
       <c r="AL7" s="1" t="inlineStr"/>
       <c r="AM7" s="1" t="inlineStr"/>
-      <c r="AN7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AO7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AP7" s="6" t="inlineStr">
+      <c r="AN7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AO7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AP7" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -2017,27 +2077,27 @@
       <c r="AR7" s="1" t="inlineStr"/>
       <c r="AS7" s="1" t="inlineStr"/>
       <c r="AT7" s="1" t="inlineStr"/>
-      <c r="AU7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AV7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AW7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AX7" s="6" t="inlineStr">
-        <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="AY7" s="6" t="inlineStr">
+      <c r="AU7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AV7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AW7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AX7" s="8" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="AY7" s="8" t="inlineStr">
         <is>
           <t>RA</t>
         </is>
@@ -2063,6 +2123,9 @@
         <v>0</v>
       </c>
       <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2073,32 +2136,32 @@
       <c r="B8" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>{291SDF-</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>(DH DL)ATL-(DH DL)[DFW20.9]</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>DFW-RFD-[DFW15.4]</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>DFW-SDF-[OAK25.2]</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>OAK-[ONT16.6]</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>ONT-DEN-SDF}</t>
         </is>
@@ -2108,79 +2171,79 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="N8" s="12" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
-      <c r="R8" s="1" t="inlineStr"/>
+      <c r="R8" s="10" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr"/>
       <c r="T8" s="1" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
+      <c r="U8" s="11" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
       <c r="W8" s="1" t="inlineStr"/>
-      <c r="X8" s="6" t="inlineStr">
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>{356SDF-</t>
         </is>
       </c>
-      <c r="Y8" s="6" t="inlineStr">
+      <c r="Y8" s="8" t="inlineStr">
         <is>
           <t>(DH AA)CLT-(DH AA)[DFW20.5]</t>
         </is>
       </c>
-      <c r="Z8" s="6" t="inlineStr">
+      <c r="Z8" s="8" t="inlineStr">
         <is>
           <t>DFW-RFD-[DFW15.8]</t>
         </is>
       </c>
-      <c r="AA8" s="6" t="inlineStr">
+      <c r="AA8" s="8" t="inlineStr">
         <is>
           <t>DFW-RFD-[DFW15.4]</t>
         </is>
       </c>
-      <c r="AB8" s="6" t="inlineStr">
+      <c r="AB8" s="8" t="inlineStr">
         <is>
           <t>DFW-SDF-[OAK25.2]</t>
         </is>
       </c>
-      <c r="AC8" s="6" t="inlineStr">
+      <c r="AC8" s="8" t="inlineStr">
         <is>
           <t>OAK-[ONT13.5]</t>
         </is>
       </c>
-      <c r="AD8" s="6" t="inlineStr">
+      <c r="AD8" s="8" t="inlineStr">
         <is>
           <t>ONT-(DH DL)ATL-(DH DL)SDF}</t>
         </is>
       </c>
       <c r="AE8" s="1" t="inlineStr"/>
       <c r="AF8" s="1" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AG8" s="1" t="inlineStr"/>
       <c r="AH8" s="1" t="inlineStr"/>
       <c r="AI8" s="1" t="inlineStr"/>
       <c r="AJ8" s="1" t="inlineStr"/>
       <c r="AK8" s="1" t="inlineStr"/>
-      <c r="AL8" s="6" t="inlineStr">
+      <c r="AL8" s="8" t="inlineStr">
         <is>
           <t>{396SDF-(DH DL)DTW-</t>
         </is>
       </c>
-      <c r="AM8" s="6" t="inlineStr">
+      <c r="AM8" s="8" t="inlineStr">
         <is>
           <t>[LAN24.1]</t>
         </is>
       </c>
-      <c r="AN8" s="6" t="inlineStr">
+      <c r="AN8" s="8" t="inlineStr">
         <is>
           <t>LAN-SDF-[LAN15.8]</t>
         </is>
       </c>
-      <c r="AO8" s="6" t="inlineStr">
+      <c r="AO8" s="8" t="inlineStr">
         <is>
           <t>LAN-SDF-[LAN15.8]</t>
         </is>
       </c>
-      <c r="AP8" s="6" t="inlineStr">
+      <c r="AP8" s="8" t="inlineStr">
         <is>
           <t>LAN-SDF-[LAN15.8]</t>
         </is>
@@ -2190,12 +2253,12 @@
           <t>LAN-SDF-[LAN15.8]</t>
         </is>
       </c>
-      <c r="AR8" s="6" t="inlineStr">
+      <c r="AR8" s="8" t="inlineStr">
         <is>
           <t>LAN-SDF-[EWR17.4]</t>
         </is>
       </c>
-      <c r="AS8" s="6" t="inlineStr">
+      <c r="AS8" s="8" t="inlineStr">
         <is>
           <t>EWR-SDF}</t>
         </is>
@@ -2207,32 +2270,32 @@
       <c r="AX8" s="1" t="inlineStr"/>
       <c r="AY8" s="1" t="inlineStr"/>
       <c r="AZ8" s="1" t="inlineStr"/>
-      <c r="BA8" s="6" t="inlineStr">
+      <c r="BA8" s="8" t="inlineStr">
         <is>
           <t>{309SDF-(DH WN)MDW-(DH WN)[MCI20.5]</t>
         </is>
       </c>
-      <c r="BB8" s="6" t="inlineStr">
+      <c r="BB8" s="8" t="inlineStr">
         <is>
           <t>MCI-SDF-[MKE15.3]</t>
         </is>
       </c>
-      <c r="BC8" s="6" t="inlineStr">
+      <c r="BC8" s="8" t="inlineStr">
         <is>
           <t>MKE-SDF-[MKE15.3]</t>
         </is>
       </c>
-      <c r="BD8" s="6" t="inlineStr">
+      <c r="BD8" s="8" t="inlineStr">
         <is>
           <t>MKE-SDF-[MKE15.3]</t>
         </is>
       </c>
-      <c r="BE8" s="6" t="inlineStr">
+      <c r="BE8" s="8" t="inlineStr">
         <is>
           <t>MKE-SDF-[MKE15.3]</t>
         </is>
       </c>
-      <c r="BF8" s="6" t="inlineStr">
+      <c r="BF8" s="8" t="inlineStr">
         <is>
           <t>MKE-SDF}</t>
         </is>
@@ -2248,9 +2311,12 @@
         <v>62.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>140.05</v>
       </c>
       <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2261,37 +2327,37 @@
       <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>{307SDF-</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>(DH WN)[ATL24.0]</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[CLE14.7]</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>CLE-SDF-[CLE14.7]</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>CLE-SDF-[CLE14.7]</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>CLE-SDF-[CLE14.7]</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>CLE-SDF}</t>
         </is>
@@ -2300,45 +2366,45 @@
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="N9" s="12" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="8" t="inlineStr">
         <is>
           <t>{400SDF-(DH DL)ATL-(DH DL)[MDT27.8]</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S9" s="6" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
         <is>
           <t>MDT-SDF-[MDT15.2]</t>
         </is>
       </c>
-      <c r="T9" s="6" t="inlineStr">
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>MDT-SDF-[MDT15.2]</t>
         </is>
       </c>
-      <c r="U9" s="9" t="inlineStr">
+      <c r="U9" s="13" t="inlineStr">
         <is>
           <t>MDT-SDF-[MDT15.2]</t>
         </is>
       </c>
-      <c r="V9" s="6" t="inlineStr">
+      <c r="V9" s="8" t="inlineStr">
         <is>
           <t>MDT-SDF-[MDT15.9]</t>
         </is>
       </c>
-      <c r="W9" s="6" t="inlineStr">
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>MDT-SDF-[MDT11.6] MDT-</t>
         </is>
       </c>
-      <c r="X9" s="6" t="inlineStr">
+      <c r="X9" s="8" t="inlineStr">
         <is>
           <t>(DH AA)CLT-(DH AA)SDF}</t>
         </is>
@@ -2349,58 +2415,58 @@
       <c r="AB9" s="1" t="inlineStr"/>
       <c r="AC9" s="1" t="inlineStr"/>
       <c r="AD9" s="1" t="inlineStr"/>
-      <c r="AE9" s="6" t="inlineStr">
+      <c r="AE9" s="8" t="inlineStr">
         <is>
           <t>{326SDF-(DH DL)[DTW26]</t>
         </is>
       </c>
-      <c r="AF9" s="6" t="inlineStr">
+      <c r="AF9" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG9" s="10" t="inlineStr">
+      <c r="AG9" s="8" t="inlineStr">
         <is>
           <t>DTW-SDF-[ATL16.9]</t>
         </is>
       </c>
-      <c r="AH9" s="6" t="inlineStr">
+      <c r="AH9" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[ATL16.9]</t>
         </is>
       </c>
-      <c r="AI9" s="6" t="inlineStr">
+      <c r="AI9" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[ATL16.9]</t>
         </is>
       </c>
-      <c r="AJ9" s="6" t="inlineStr">
+      <c r="AJ9" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[MIA14.7]</t>
         </is>
       </c>
-      <c r="AK9" s="6" t="inlineStr">
+      <c r="AK9" s="8" t="inlineStr">
         <is>
           <t>MIA-SDF}</t>
         </is>
       </c>
       <c r="AL9" s="1" t="inlineStr"/>
-      <c r="AM9" s="6" t="inlineStr">
+      <c r="AM9" s="8" t="inlineStr">
         <is>
           <t>{338SDF-(DH AA)[DFW14.8]</t>
         </is>
       </c>
-      <c r="AN9" s="6" t="inlineStr">
+      <c r="AN9" s="8" t="inlineStr">
         <is>
           <t>DFW-[PHL31.6]</t>
         </is>
       </c>
-      <c r="AO9" s="6" t="inlineStr">
+      <c r="AO9" s="8" t="inlineStr">
         <is>
           <t>PHL-</t>
         </is>
       </c>
-      <c r="AP9" s="6" t="inlineStr">
+      <c r="AP9" s="8" t="inlineStr">
         <is>
           <t>SDF-[ORD16.6]</t>
         </is>
@@ -2410,12 +2476,12 @@
           <t>ORD-SDF-[MCO14.6]</t>
         </is>
       </c>
-      <c r="AR9" s="6" t="inlineStr">
+      <c r="AR9" s="8" t="inlineStr">
         <is>
           <t>MCO-SDF-[CLE12.6] CLE-</t>
         </is>
       </c>
-      <c r="AS9" s="6" t="inlineStr">
+      <c r="AS9" s="8" t="inlineStr">
         <is>
           <t>(DH WN)MDW-(DH WN)SDF}</t>
         </is>
@@ -2444,9 +2510,12 @@
         <v>75</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>143.28</v>
       </c>
       <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2457,42 +2526,42 @@
       <c r="B10" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>{395SDF-(DH DL)[ATL25.5]</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[ATL16.9]</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[ATL16.9]</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[ATL16.9]</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>ATL-SDF-[MCO14.6]</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>MCO-SDF-[EWR17.4]</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>EWR-SDF}</t>
         </is>
@@ -2500,103 +2569,103 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" s="12" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
-      <c r="R10" s="1" t="inlineStr"/>
+      <c r="R10" s="10" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr"/>
       <c r="T10" s="1" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
+      <c r="U10" s="11" t="inlineStr"/>
       <c r="V10" s="1" t="inlineStr"/>
       <c r="W10" s="1" t="inlineStr"/>
-      <c r="X10" s="6" t="inlineStr">
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>{310SDF-</t>
         </is>
       </c>
-      <c r="Y10" s="6" t="inlineStr">
+      <c r="Y10" s="8" t="inlineStr">
         <is>
           <t>(DH AA)CLT-(DH AA)[RDU20.0]</t>
         </is>
       </c>
-      <c r="Z10" s="6" t="inlineStr">
+      <c r="Z10" s="8" t="inlineStr">
         <is>
           <t>RDU-SDF-[RDU14.5]</t>
         </is>
       </c>
-      <c r="AA10" s="6" t="inlineStr">
+      <c r="AA10" s="8" t="inlineStr">
         <is>
           <t>RDU-SDF-[RDU14.5]</t>
         </is>
       </c>
-      <c r="AB10" s="6" t="inlineStr">
+      <c r="AB10" s="8" t="inlineStr">
         <is>
           <t>RDU-SDF-[RDU14.5]</t>
         </is>
       </c>
-      <c r="AC10" s="6" t="inlineStr">
+      <c r="AC10" s="8" t="inlineStr">
         <is>
           <t>RDU-SDF-[RDU9.8] RDU-(DH AA)CLT-(DH AA)SDF}</t>
         </is>
       </c>
       <c r="AD10" s="1" t="inlineStr"/>
-      <c r="AE10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AF10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AG10" s="10" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AH10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AI10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AK10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AL10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AM10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AN10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AO10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AP10" s="6" t="inlineStr">
+      <c r="AE10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AF10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AG10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AH10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AI10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AJ10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AK10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AL10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AM10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AN10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AO10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AP10" s="8" t="inlineStr">
         <is>
           <t>VTO</t>
         </is>
@@ -2606,77 +2675,77 @@
           <t>VTO</t>
         </is>
       </c>
-      <c r="AR10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AS10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AT10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AU10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AV10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AW10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AX10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AY10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AZ10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BA10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BB10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BC10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BD10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BE10" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BF10" s="6" t="inlineStr">
+      <c r="AR10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AS10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AT10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AU10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AV10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AW10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AX10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AY10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AZ10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BA10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BB10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BC10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BD10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BE10" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BF10" s="8" t="inlineStr">
         <is>
           <t>VTO</t>
         </is>
@@ -2692,9 +2761,12 @@
         <v>75</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2705,160 +2777,160 @@
       <c r="B11" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="U11" s="9" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="V11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="W11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="Y11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="Z11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AA11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AB11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AC11" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AD11" s="6" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="R11" s="15" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="U11" s="13" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="Z11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AA11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AB11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AC11" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AD11" s="8" t="inlineStr">
         <is>
           <t>VTO</t>
         </is>
       </c>
       <c r="AE11" s="1" t="inlineStr"/>
       <c r="AF11" s="1" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="6" t="inlineStr">
+      <c r="AG11" s="1" t="inlineStr"/>
+      <c r="AH11" s="8" t="inlineStr">
         <is>
           <t>{600SDF-</t>
         </is>
       </c>
-      <c r="AI11" s="6" t="inlineStr">
+      <c r="AI11" s="8" t="inlineStr">
         <is>
           <t>[HNL20.6]</t>
         </is>
       </c>
-      <c r="AJ11" s="6" t="inlineStr">
+      <c r="AJ11" s="8" t="inlineStr">
         <is>
           <t>HNL-(DH DL)ATL-(DH DL)SDF}</t>
         </is>
@@ -2868,7 +2940,7 @@
       <c r="AM11" s="1" t="inlineStr"/>
       <c r="AN11" s="1" t="inlineStr"/>
       <c r="AO11" s="1" t="inlineStr"/>
-      <c r="AP11" s="6" t="inlineStr">
+      <c r="AP11" s="8" t="inlineStr">
         <is>
           <t>{600SDF-</t>
         </is>
@@ -2878,7 +2950,7 @@
           <t>[HNL20.6]</t>
         </is>
       </c>
-      <c r="AR11" s="6" t="inlineStr">
+      <c r="AR11" s="8" t="inlineStr">
         <is>
           <t>HNL-(DH DL)ATL-(DH DL)SDF}</t>
         </is>
@@ -2887,17 +2959,17 @@
       <c r="AT11" s="1" t="inlineStr"/>
       <c r="AU11" s="1" t="inlineStr"/>
       <c r="AV11" s="1" t="inlineStr"/>
-      <c r="AW11" s="6" t="inlineStr">
+      <c r="AW11" s="8" t="inlineStr">
         <is>
           <t>{601SDF-</t>
         </is>
       </c>
-      <c r="AX11" s="6" t="inlineStr">
+      <c r="AX11" s="8" t="inlineStr">
         <is>
           <t>[HNL20.6]</t>
         </is>
       </c>
-      <c r="AY11" s="6" t="inlineStr">
+      <c r="AY11" s="8" t="inlineStr">
         <is>
           <t>HNL-(DH DL)ATL-(DH DL)SDF}</t>
         </is>
@@ -2907,17 +2979,17 @@
       <c r="BB11" s="1" t="inlineStr"/>
       <c r="BC11" s="1" t="inlineStr"/>
       <c r="BD11" s="1" t="inlineStr"/>
-      <c r="BE11" s="6" t="inlineStr">
+      <c r="BE11" s="8" t="inlineStr">
         <is>
           <t>{612SDF-(C,DH UPS)CGN-[FRA25.1]</t>
         </is>
       </c>
-      <c r="BF11" s="6" t="inlineStr">
+      <c r="BF11" s="8" t="inlineStr">
         <is>
           <t>FRA-</t>
         </is>
       </c>
-      <c r="BG11" s="6" t="inlineStr">
+      <c r="BG11" s="8" t="inlineStr">
         <is>
           <t>(DH EK)DXB-(DH EK)[BAH17.6] BAH-</t>
         </is>
@@ -2932,9 +3004,12 @@
         <v>37.5</v>
       </c>
       <c r="BK11" t="n">
+        <v>69.97</v>
+      </c>
+      <c r="BL11" t="n">
         <v>439</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BM11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2945,202 +3020,202 @@
       <c r="B12" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="U12" s="9" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="W12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="X12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="Y12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="Z12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AB12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AC12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AD12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AE12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AF12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AG12" s="10" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AH12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AI12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AJ12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AK12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AL12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AM12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AN12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AO12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AP12" s="6" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="R12" s="15" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="U12" s="13" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AB12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AC12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AD12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AG12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AH12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AI12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AJ12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AK12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AL12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AN12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AO12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AP12" s="8" t="inlineStr">
         <is>
           <t>VTO</t>
         </is>
@@ -3150,77 +3225,77 @@
           <t>VTO</t>
         </is>
       </c>
-      <c r="AR12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AS12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AT12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AU12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AV12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AY12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="AZ12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BA12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BB12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BC12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BD12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BE12" s="6" t="inlineStr">
-        <is>
-          <t>VTO</t>
-        </is>
-      </c>
-      <c r="BF12" s="6" t="inlineStr">
+      <c r="AR12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AS12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AW12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AX12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AY12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="AZ12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BA12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BB12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>VTO</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
         <is>
           <t>VTO</t>
         </is>
@@ -3239,6 +3314,9 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3249,22 +3327,22 @@
       <c r="B13" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3272,27 +3350,27 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3300,33 +3378,33 @@
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
-      <c r="R13" s="1" t="inlineStr"/>
+      <c r="R13" s="10" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr"/>
       <c r="T13" s="1" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr"/>
+      <c r="U13" s="11" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr"/>
       <c r="W13" s="1" t="inlineStr"/>
-      <c r="X13" s="6" t="inlineStr">
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="Y13" s="6" t="inlineStr">
+      <c r="Y13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="Z13" s="6" t="inlineStr">
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
+      <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AB13" s="6" t="inlineStr">
+      <c r="AB13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3335,27 +3413,27 @@
       <c r="AD13" s="1" t="inlineStr"/>
       <c r="AE13" s="1" t="inlineStr"/>
       <c r="AF13" s="1" t="inlineStr"/>
-      <c r="AG13" s="10" t="inlineStr">
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AH13" s="6" t="inlineStr">
+      <c r="AH13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AI13" s="6" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AJ13" s="6" t="inlineStr">
+      <c r="AJ13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AK13" s="6" t="inlineStr">
+      <c r="AK13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3370,22 +3448,22 @@
           <t>RB</t>
         </is>
       </c>
-      <c r="AR13" s="6" t="inlineStr">
+      <c r="AR13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AS13" s="6" t="inlineStr">
+      <c r="AS13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AT13" s="6" t="inlineStr">
+      <c r="AT13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AU13" s="6" t="inlineStr">
+      <c r="AU13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3393,22 +3471,22 @@
       <c r="AV13" s="1" t="inlineStr"/>
       <c r="AW13" s="1" t="inlineStr"/>
       <c r="AX13" s="1" t="inlineStr"/>
-      <c r="AY13" s="6" t="inlineStr">
+      <c r="AY13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="AZ13" s="6" t="inlineStr">
+      <c r="AZ13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="BA13" s="6" t="inlineStr">
+      <c r="BA13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
-      <c r="BB13" s="6" t="inlineStr">
+      <c r="BB13" s="8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3433,6 +3511,9 @@
       <c r="BL13" t="n">
         <v>0</v>
       </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" t="n">
@@ -3441,37 +3522,37 @@
       <c r="B14" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -3480,40 +3561,40 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" s="12" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="U14" s="9" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="W14" s="6" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="R14" s="15" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="U14" s="13" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -3525,37 +3606,37 @@
       <c r="AB14" s="1" t="inlineStr"/>
       <c r="AC14" s="1" t="inlineStr"/>
       <c r="AD14" s="1" t="inlineStr"/>
-      <c r="AE14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AF14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AG14" s="10" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AH14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AI14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AJ14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AK14" s="6" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AH14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AI14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AJ14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AK14" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -3565,39 +3646,39 @@
       <c r="AN14" s="1" t="inlineStr"/>
       <c r="AO14" s="1" t="inlineStr"/>
       <c r="AP14" s="1" t="inlineStr"/>
-      <c r="AQ14" s="5" t="inlineStr"/>
+      <c r="AQ14" s="1" t="inlineStr"/>
       <c r="AR14" s="1" t="inlineStr"/>
-      <c r="AS14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AT14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AU14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AV14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
+      <c r="AS14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AV14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AW14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AX14" s="8" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="AY14" s="8" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -3625,6 +3706,9 @@
       <c r="BL14" t="n">
         <v>0</v>
       </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" t="n">
@@ -3633,37 +3717,37 @@
       <c r="B15" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3672,40 +3756,40 @@
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" s="12" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="W15" s="6" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="R15" s="15" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="U15" s="13" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3717,37 +3801,37 @@
       <c r="AB15" s="1" t="inlineStr"/>
       <c r="AC15" s="1" t="inlineStr"/>
       <c r="AD15" s="1" t="inlineStr"/>
-      <c r="AE15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AF15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AG15" s="10" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AH15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AI15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AJ15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AK15" s="6" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AH15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AI15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AJ15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3757,39 +3841,39 @@
       <c r="AN15" s="1" t="inlineStr"/>
       <c r="AO15" s="1" t="inlineStr"/>
       <c r="AP15" s="1" t="inlineStr"/>
-      <c r="AQ15" s="5" t="inlineStr"/>
+      <c r="AQ15" s="1" t="inlineStr"/>
       <c r="AR15" s="1" t="inlineStr"/>
-      <c r="AS15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AT15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AU15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AV15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
+      <c r="AS15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AW15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AX15" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AY15" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3817,6 +3901,9 @@
       <c r="BL15" t="n">
         <v>0</v>
       </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" t="n">
@@ -3825,32 +3912,32 @@
       <c r="B16" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3860,66 +3947,66 @@
       <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="R16" s="15" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
       <c r="S16" s="1" t="inlineStr"/>
       <c r="T16" s="1" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
+      <c r="U16" s="11" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr"/>
       <c r="W16" s="1" t="inlineStr"/>
       <c r="X16" s="1" t="inlineStr"/>
       <c r="Y16" s="1" t="inlineStr"/>
       <c r="Z16" s="1" t="inlineStr"/>
       <c r="AA16" s="1" t="inlineStr"/>
-      <c r="AB16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AC16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AE16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AF16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AG16" s="10" t="inlineStr">
+      <c r="AB16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AC16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AD16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3930,17 +4017,17 @@
       <c r="AK16" s="1" t="inlineStr"/>
       <c r="AL16" s="1" t="inlineStr"/>
       <c r="AM16" s="1" t="inlineStr"/>
-      <c r="AN16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AO16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="AP16" s="6" t="inlineStr">
+      <c r="AN16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AO16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="AP16" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3950,7 +4037,7 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="AR16" s="6" t="inlineStr">
+      <c r="AR16" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -3962,32 +4049,32 @@
       <c r="AW16" s="1" t="inlineStr"/>
       <c r="AX16" s="1" t="inlineStr"/>
       <c r="AY16" s="1" t="inlineStr"/>
-      <c r="AZ16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BA16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BB16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BC16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BD16" s="6" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="BE16" s="6" t="inlineStr">
+      <c r="AZ16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BA16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BB16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
@@ -4009,6 +4096,9 @@
       <c r="BL16" t="n">
         <v>0</v>
       </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" t="n">
@@ -4017,202 +4107,202 @@
       <c r="B17" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="U17" s="9" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="W17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="X17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="Y17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="Z17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AB17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AC17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AE17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AF17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AG17" s="10" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AH17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AI17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AJ17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AK17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AL17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AN17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AO17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AP17" s="6" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="R17" s="15" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="U17" s="13" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AB17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AC17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AD17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AG17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AH17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AI17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AJ17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AK17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AL17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AM17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AN17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AO17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AP17" s="8" t="inlineStr">
         <is>
           <t>VOR</t>
         </is>
@@ -4222,77 +4312,77 @@
           <t>VOR</t>
         </is>
       </c>
-      <c r="AR17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AS17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AT17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AU17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AV17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AY17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="AZ17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="BA17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="BB17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="BC17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="BD17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="BE17" s="6" t="inlineStr">
-        <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="BF17" s="6" t="inlineStr">
+      <c r="AR17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AS17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AT17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AU17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AV17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AW17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AX17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AY17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="AZ17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="BA17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="BB17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
         <is>
           <t>VOR</t>
         </is>
@@ -4313,9 +4403,12 @@
       <c r="BL17" t="n">
         <v>0</v>
       </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL17"/>
+  <autoFilter ref="A1:BM17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
